--- a/dc3_milk_run_routes.xlsx
+++ b/dc3_milk_run_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,14 +493,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI66078 -&gt; DPI66658 -&gt; DPI67187 -&gt; DPI70105 -&gt; DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI66574 -&gt; DPI64136</t>
+          <t>DPI70051 -&gt; DPI63862 -&gt; DPI64235 -&gt; DPI66487 -&gt; DPI64424 -&gt; DPI70014 -&gt; DPI64040 -&gt; DPI66332 -&gt; DPI64190 -&gt; DPI67069</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +509,13 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.08</v>
       </c>
       <c r="I2" t="n">
-        <v>873.41</v>
+        <v>270</v>
       </c>
       <c r="J2" t="n">
-        <v>1275484.53</v>
+        <v>1077508.06</v>
       </c>
     </row>
     <row r="3">
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI70047 -&gt; DPI66679 -&gt; DPI64431 -&gt; DPI66653</t>
+          <t>DFT80016 -&gt; DPI63872 -&gt; DPI70129 -&gt; DPI63871 -&gt; DPI64610 -&gt; DPI67235 -&gt; DPI67252 -&gt; DFT80069 -&gt; DPI70182</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>935</v>
+        <v>895</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>95.41</v>
+        <v>91.33</v>
       </c>
       <c r="I3" t="n">
-        <v>718.0599999999999</v>
+        <v>1374.11</v>
       </c>
       <c r="J3" t="n">
-        <v>1224515.9</v>
+        <v>1439766</v>
       </c>
     </row>
     <row r="4">
@@ -569,14 +569,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI64480 -&gt; DPI64433 -&gt; DPI67148 -&gt; DPI64742 -&gt; DPI63976 -&gt; DPI70296 -&gt; DPI67180 -&gt; DPI64634 -&gt; DPI67224</t>
+          <t>DPI66035 -&gt; DPI64594 -&gt; DPI70321 -&gt; DPI66904 -&gt; DPI64030 -&gt; DPI64286 -&gt; DPI64349 -&gt; DPI64084</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>903</v>
+        <v>961</v>
       </c>
       <c r="F4" t="n">
         <v>1613</v>
@@ -585,13 +585,13 @@
         <v>980</v>
       </c>
       <c r="H4" t="n">
-        <v>92.14</v>
+        <v>98.06</v>
       </c>
       <c r="I4" t="n">
-        <v>983.1799999999999</v>
+        <v>1382.23</v>
       </c>
       <c r="J4" t="n">
-        <v>1311503</v>
+        <v>1442431.02</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI64495 -&gt; DFT80080 -&gt; DPI66129 -&gt; DPI66736 -&gt; DPI70229 -&gt; DPI64018 -&gt; DPI66096</t>
+          <t>DFT80025 -&gt; DPI70126 -&gt; DPI64717 -&gt; DPI66290 -&gt; DPI66008 -&gt; DPI66507 -&gt; DPI66463 -&gt; DPI64181</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>945</v>
+        <v>978</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>96.43000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1258.36</v>
+        <v>265.49</v>
       </c>
       <c r="J5" t="n">
-        <v>1401787.42</v>
+        <v>1076028.25</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI67178 -&gt; DPI64297 -&gt; DPI64724 -&gt; DPI63915 -&gt; DPI66742 -&gt; DPI66067 -&gt; DPI70213</t>
+          <t>DPI67040 -&gt; DPI63905 -&gt; DPI64204</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>843</v>
+        <v>956</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>86.02</v>
+        <v>97.55</v>
       </c>
       <c r="I6" t="n">
-        <v>841.62</v>
+        <v>1022.74</v>
       </c>
       <c r="J6" t="n">
-        <v>1265054.84</v>
+        <v>1324482.34</v>
       </c>
     </row>
     <row r="7">
@@ -683,29 +683,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI70142 -&gt; DPI70109 -&gt; DPI66634 -&gt; DPI70214 -&gt; DPI64548 -&gt; DPI70107</t>
+          <t>DPI63843 -&gt; DPI63834</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>463</v>
+        <v>911</v>
       </c>
       <c r="F7" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="G7" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>70.15000000000001</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1345.56</v>
+        <v>967.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1244215.15</v>
+        <v>1306227.04</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI64638 -&gt; DPI66307 -&gt; DPI66039 -&gt; DPI64450 -&gt; DPI67121 -&gt; DPI66597 -&gt; DPI66179 -&gt; DPI64052</t>
+          <t>DPI64205</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>908</v>
+        <v>980</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,203 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>92.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>207.71</v>
+        <v>780.3200000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1057068.33</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DC_3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DPI66339 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI70255 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094 -&gt; DFT80088 -&gt; DPI64216 -&gt; DPI70316</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="n">
-        <v>948</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G9" t="n">
-        <v>980</v>
-      </c>
-      <c r="H9" t="n">
-        <v>96.73</v>
-      </c>
-      <c r="I9" t="n">
-        <v>592.5599999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1183340.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DC_3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DPI66387 -&gt; DPI64301 -&gt; DPI66069 -&gt; DPI64039 -&gt; DPI66289 -&gt; DPI66203 -&gt; DPI63958</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>837</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G10" t="n">
-        <v>980</v>
-      </c>
-      <c r="H10" t="n">
-        <v>85.41</v>
-      </c>
-      <c r="I10" t="n">
-        <v>195.95</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1053210.66</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DC_3</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI64666 -&gt; DPI66209 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" t="n">
-        <v>956</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G11" t="n">
-        <v>980</v>
-      </c>
-      <c r="H11" t="n">
-        <v>97.55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>940.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1297365.99</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DC_3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>DPI66221 -&gt; DPI64196 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI66449 -&gt; DPI63919 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66373</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>949</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G12" t="n">
-        <v>980</v>
-      </c>
-      <c r="H12" t="n">
-        <v>96.84</v>
-      </c>
-      <c r="I12" t="n">
-        <v>429.73</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1129914.31</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DC_3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DPI66715 -&gt; DPI64169 -&gt; DPI66051 -&gt; DPI63802 -&gt; DPI64057 -&gt; DPI66172 -&gt; DPI64037 -&gt; DPI70096 -&gt; DPI64413 -&gt; DPI66645 -&gt; DPI64686 -&gt; DPI64218</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" t="n">
-        <v>980</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G13" t="n">
-        <v>980</v>
-      </c>
-      <c r="H13" t="n">
-        <v>100</v>
-      </c>
-      <c r="I13" t="n">
-        <v>913.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1288738.57</v>
+        <v>1244942.83</v>
       </c>
     </row>
   </sheetData>

--- a/dc3_milk_run_routes.xlsx
+++ b/dc3_milk_run_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,14 +493,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI70051 -&gt; DPI63862 -&gt; DPI64235 -&gt; DPI66487 -&gt; DPI64424 -&gt; DPI70014 -&gt; DPI64040 -&gt; DPI66332 -&gt; DPI64190 -&gt; DPI67069</t>
+          <t>DPI70129 -&gt; DPI63871 -&gt; DPI64610 -&gt; DPI64205 -&gt; DPI67235 -&gt; DPI67252 -&gt; DFT80069 -&gt; DPI63843 -&gt; DPI63834</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +509,13 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>99.08</v>
+        <v>99.69</v>
       </c>
       <c r="I2" t="n">
-        <v>270</v>
+        <v>1238.23</v>
       </c>
       <c r="J2" t="n">
-        <v>1077508.06</v>
+        <v>1395183.69</v>
       </c>
     </row>
     <row r="3">
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DFT80016 -&gt; DPI63872 -&gt; DPI70129 -&gt; DPI63871 -&gt; DPI64610 -&gt; DPI67235 -&gt; DPI67252 -&gt; DFT80069 -&gt; DPI70182</t>
+          <t>DPI64424 -&gt; DPI66290 -&gt; DPI64717 -&gt; DPI70126 -&gt; DFT80025 -&gt; DPI66487 -&gt; DPI64235 -&gt; DPI63862 -&gt; DPI70051 -&gt; DPI66035 -&gt; DPI64594</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>895</v>
+        <v>810</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>91.33</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1374.11</v>
+        <v>262.82</v>
       </c>
       <c r="J3" t="n">
-        <v>1439766</v>
+        <v>1075152.5</v>
       </c>
     </row>
     <row r="4">
@@ -569,14 +569,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI66035 -&gt; DPI64594 -&gt; DPI70321 -&gt; DPI66904 -&gt; DPI64030 -&gt; DPI64286 -&gt; DPI64349 -&gt; DPI64084</t>
+          <t>DFT80016 -&gt; DPI63872 -&gt; DPI64181 -&gt; DPI66463 -&gt; DPI66507</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>961</v>
+        <v>702</v>
       </c>
       <c r="F4" t="n">
         <v>1613</v>
@@ -585,13 +585,13 @@
         <v>980</v>
       </c>
       <c r="H4" t="n">
-        <v>98.06</v>
+        <v>71.63</v>
       </c>
       <c r="I4" t="n">
-        <v>1382.23</v>
+        <v>209.79</v>
       </c>
       <c r="J4" t="n">
-        <v>1442431.02</v>
+        <v>1057752.83</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DFT80025 -&gt; DPI70126 -&gt; DPI64717 -&gt; DPI66290 -&gt; DPI66008 -&gt; DPI66507 -&gt; DPI66463 -&gt; DPI64181</t>
+          <t>DPI70182 -&gt; DPI64204 -&gt; DPI63905</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>978</v>
+        <v>799</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>99.8</v>
+        <v>81.53</v>
       </c>
       <c r="I5" t="n">
-        <v>265.49</v>
+        <v>1085.29</v>
       </c>
       <c r="J5" t="n">
-        <v>1076028.25</v>
+        <v>1345003.83</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI67040 -&gt; DPI63905 -&gt; DPI64204</t>
+          <t>DPI67040 -&gt; DPI70321 -&gt; DPI66904 -&gt; DPI64030 -&gt; DPI64286 -&gt; DPI64349 -&gt; DPI64084</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>956</v>
+        <v>834</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>97.55</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1022.74</v>
+        <v>1213.85</v>
       </c>
       <c r="J6" t="n">
-        <v>1324482.34</v>
+        <v>1387184.02</v>
       </c>
     </row>
     <row r="7">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI63843 -&gt; DPI63834</t>
+          <t>DPI66008 -&gt; DPI70014 -&gt; DPI64040 -&gt; DPI66332 -&gt; DPI64190 -&gt; DPI67069</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>911</v>
+        <v>815</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,51 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>92.95999999999999</v>
+        <v>83.16</v>
       </c>
       <c r="I7" t="n">
-        <v>967.1</v>
+        <v>210.51</v>
       </c>
       <c r="J7" t="n">
-        <v>1306227.04</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DC_3</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DPI64205</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>980</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G8" t="n">
-        <v>980</v>
-      </c>
-      <c r="H8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I8" t="n">
-        <v>780.3200000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1244942.83</v>
+        <v>1057988.32</v>
       </c>
     </row>
   </sheetData>

--- a/dc3_milk_run_routes.xlsx
+++ b/dc3_milk_run_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,16 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>fixed_cost</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>variable_cost_per_km</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>monthly_cost</t>
         </is>
       </c>
@@ -515,7 +525,13 @@
         <v>1238.23</v>
       </c>
       <c r="J2" t="n">
-        <v>1395183.69</v>
+        <v>98892</v>
+      </c>
+      <c r="K2" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L2" t="n">
+        <v>505155.69</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +569,13 @@
         <v>262.82</v>
       </c>
       <c r="J3" t="n">
-        <v>1075152.5</v>
+        <v>98892</v>
+      </c>
+      <c r="K3" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L3" t="n">
+        <v>185124.5</v>
       </c>
     </row>
     <row r="4">
@@ -591,7 +613,13 @@
         <v>209.79</v>
       </c>
       <c r="J4" t="n">
-        <v>1057752.83</v>
+        <v>98892</v>
+      </c>
+      <c r="K4" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L4" t="n">
+        <v>167724.83</v>
       </c>
     </row>
     <row r="5">
@@ -629,7 +657,13 @@
         <v>1085.29</v>
       </c>
       <c r="J5" t="n">
-        <v>1345003.83</v>
+        <v>98892</v>
+      </c>
+      <c r="K5" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L5" t="n">
+        <v>454975.83</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +701,13 @@
         <v>1213.85</v>
       </c>
       <c r="J6" t="n">
-        <v>1387184.02</v>
+        <v>98892</v>
+      </c>
+      <c r="K6" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L6" t="n">
+        <v>497156.02</v>
       </c>
     </row>
     <row r="7">
@@ -705,7 +745,13 @@
         <v>210.51</v>
       </c>
       <c r="J7" t="n">
-        <v>1057988.32</v>
+        <v>98892</v>
+      </c>
+      <c r="K7" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L7" t="n">
+        <v>167960.32</v>
       </c>
     </row>
   </sheetData>
